--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.169.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.169.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0169.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0169.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 54 to 60</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L3: isolated marker/symbol line :: 2</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: C</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 60</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54 â€” 55</t>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 54 to 64</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 60</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: I</t>
+          <t>L34: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -691,7 +699,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 64</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -727,12 +739,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54â€”55</t>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 64</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +756,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: I</t>
+          <t>L36: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,7 +782,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -786,12 +798,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 55â€”56â€”57</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -803,7 +815,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: i</t>
+          <t>L37: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -843,14 +855,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -862,7 +870,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: J</t>
+          <t>L38: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -898,14 +906,10 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 107 â€” 108</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 57â€”58</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -917,7 +921,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 54</t>
+          <t>L39: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -956,7 +960,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58â€”59</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -968,7 +972,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 64</t>
+          <t>L43: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1007,7 +1011,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1019,7 +1023,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 54</t>
+          <t>L45: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1041,12 +1045,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1058,19 +1062,19 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 54</t>
+          <t>L25: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 54</t>
+          <t>L47: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1097,7 +1101,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1109,19 +1113,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: 0</t>
+          <t>L27: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 64</t>
+          <t>L49: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1143,12 +1147,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1160,19 +1164,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: -</t>
+          <t>L31: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L53: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1211,19 +1215,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: 64</t>
+          <t>L32: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: ]</t>
+          <t>L55: symbol-only separator/garbage line :: 54—55</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1250,7 +1254,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1262,19 +1266,19 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L37: symbol-only separator/garbage line :: 55-56-57</t>
+          <t>L33: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 60</t>
+          <t>L57: symbol-only separator/garbage line :: 55—56—57</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1311,21 +1315,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: .</t>
+          <t>L35: symbol-only separator/garbage line :: 54 — 55</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 63</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1362,21 +1362,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 107â€”108</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: 57-58</t>
+          <t>L37: symbol-only separator/garbage line :: 55-56-57</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 58</t>
+          <t>L63: isolated marker/symbol line :: ]</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1413,21 +1409,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L39: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 61</t>
+          <t>L65: symbol-only separator/garbage line :: 57—58</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1452,21 +1444,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 60</t>
+          <t>L40: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L78: symbol-only separator/garbage line :: .62</t>
+          <t>L67: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1491,21 +1479,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Question as to the Jurisdiction of the Court of Chancery 8â€”9</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 62</t>
+          <t>L69: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1535,12 +1519,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 63</t>
+          <t>L43: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 62</t>
+          <t>L71: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1570,12 +1554,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 58</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L73: symbol-only separator/garbage line :: 58—59</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1605,12 +1589,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 61</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1640,12 +1624,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 62</t>
+          <t>L47: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L78: symbol-only separator/garbage line :: .62</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1675,12 +1659,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 62</t>
+          <t>L49: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1710,12 +1694,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 62</t>
+          <t>L51: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1745,12 +1729,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 8</t>
+          <t>L55: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1780,12 +1764,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 8</t>
+          <t>L61: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1813,10 +1797,14 @@
       <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>L63: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 8</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1844,10 +1832,14 @@
       <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>L65: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 8</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1875,10 +1867,14 @@
       <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>L68: symbol-only separator/garbage line :: 107 — 108</t>
+        </is>
+      </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1906,10 +1902,14 @@
       <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>L74: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1923,6 +1923,196 @@
       <c r="X31" s="1" t="inlineStr"/>
       <c r="Y31" s="1" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr"/>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
+      <c r="L32" s="1" t="inlineStr"/>
+      <c r="M32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>L76: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="inlineStr"/>
+      <c r="V32" s="1" t="inlineStr"/>
+      <c r="W32" s="1" t="inlineStr"/>
+      <c r="X32" s="1" t="inlineStr"/>
+      <c r="Y32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr"/>
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr"/>
+      <c r="D33" s="1" t="inlineStr"/>
+      <c r="E33" s="1" t="inlineStr"/>
+      <c r="F33" s="1" t="inlineStr"/>
+      <c r="G33" s="1" t="inlineStr"/>
+      <c r="H33" s="1" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr"/>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
+      <c r="L33" s="1" t="inlineStr"/>
+      <c r="M33" s="1" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr"/>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>L130: symbol-only separator/garbage line :: 107—108</t>
+        </is>
+      </c>
+      <c r="P33" s="1" t="inlineStr"/>
+      <c r="Q33" s="1" t="inlineStr"/>
+      <c r="R33" s="1" t="inlineStr"/>
+      <c r="S33" s="1" t="inlineStr"/>
+      <c r="T33" s="1" t="inlineStr"/>
+      <c r="U33" s="1" t="inlineStr"/>
+      <c r="V33" s="1" t="inlineStr"/>
+      <c r="W33" s="1" t="inlineStr"/>
+      <c r="X33" s="1" t="inlineStr"/>
+      <c r="Y33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr"/>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L138: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
+      <c r="V34" s="1" t="inlineStr"/>
+      <c r="W34" s="1" t="inlineStr"/>
+      <c r="X34" s="1" t="inlineStr"/>
+      <c r="Y34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr"/>
+      <c r="C35" s="1" t="inlineStr"/>
+      <c r="D35" s="1" t="inlineStr"/>
+      <c r="E35" s="1" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr"/>
+      <c r="H35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr"/>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
+      <c r="L35" s="1" t="inlineStr"/>
+      <c r="M35" s="1" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr"/>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>L140: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="P35" s="1" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr"/>
+      <c r="R35" s="1" t="inlineStr"/>
+      <c r="S35" s="1" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr"/>
+      <c r="V35" s="1" t="inlineStr"/>
+      <c r="W35" s="1" t="inlineStr"/>
+      <c r="X35" s="1" t="inlineStr"/>
+      <c r="Y35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
+      <c r="L36" s="1" t="inlineStr"/>
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr"/>
+      <c r="V36" s="1" t="inlineStr"/>
+      <c r="W36" s="1" t="inlineStr"/>
+      <c r="X36" s="1" t="inlineStr"/>
+      <c r="Y36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr"/>
+      <c r="B37" s="1" t="inlineStr"/>
+      <c r="C37" s="1" t="inlineStr"/>
+      <c r="D37" s="1" t="inlineStr"/>
+      <c r="E37" s="1" t="inlineStr"/>
+      <c r="F37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr"/>
+      <c r="H37" s="1" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr"/>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
+      <c r="L37" s="1" t="inlineStr"/>
+      <c r="M37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr"/>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="inlineStr"/>
+      <c r="R37" s="1" t="inlineStr"/>
+      <c r="S37" s="1" t="inlineStr"/>
+      <c r="T37" s="1" t="inlineStr"/>
+      <c r="U37" s="1" t="inlineStr"/>
+      <c r="V37" s="1" t="inlineStr"/>
+      <c r="W37" s="1" t="inlineStr"/>
+      <c r="X37" s="1" t="inlineStr"/>
+      <c r="Y37" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
